--- a/output/pdf_financials_xlsx/EPF.xlsx
+++ b/output/pdf_financials_xlsx/EPF.xlsx
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.150743</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.217154</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.174921</v>
       </c>
     </row>
     <row r="35">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.150743</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.217154</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.174921</v>
       </c>
     </row>
     <row r="37">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
